--- a/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42A14D0-F535-4B6C-B2F4-E05F00EADCB1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF6AD14A-9A28-49D2-B7BC-11F3A7F7CAAF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3399,7 +3399,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="19">
-        <v>46028</v>
+        <v>46060</v>
       </c>
       <c r="D34" s="20" t="s">
         <v>68</v>
@@ -3416,18 +3416,21 @@
       </c>
       <c r="I34" s="20"/>
       <c r="J34" s="20"/>
-      <c r="K34" s="21"/>
+      <c r="K34" s="21">
+        <f>8640+23976+143856+11988+9072</f>
+        <v>197532</v>
+      </c>
       <c r="M34" s="21">
         <f t="shared" ref="M34:M53" si="8">O34*12</f>
-        <v>0</v>
+        <v>21164.142857142855</v>
       </c>
       <c r="N34" s="27">
         <f>K34-M34</f>
-        <v>0</v>
+        <v>176367.85714285716</v>
       </c>
       <c r="O34" s="33">
         <f t="shared" ref="O34:O53" si="9">K34/112</f>
-        <v>0</v>
+        <v>1763.6785714285713</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
@@ -4064,7 +4067,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>0</v>
+        <v>197532</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4072,15 +4075,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>0</v>
+        <v>21164.142857142855</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>0</v>
+        <v>176367.85714285716</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>0</v>
+        <v>1763.6785714285713</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">

--- a/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF6AD14A-9A28-49D2-B7BC-11F3A7F7CAAF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5112D3EC-FBC8-4859-A96B-082573D3CAB5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="89">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -257,9 +257,6 @@
     <t>NO</t>
   </si>
   <si>
-    <t>166-562-025-0000</t>
-  </si>
-  <si>
     <t>06/16/2026</t>
   </si>
   <si>
@@ -297,6 +294,12 @@
   </si>
   <si>
     <t>DISCOUNT</t>
+  </si>
+  <si>
+    <t>R02</t>
+  </si>
+  <si>
+    <t>166-562-025-0005</t>
   </si>
 </sst>
 </file>
@@ -2321,12 +2324,12 @@
     </row>
     <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C3" s="41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" s="42"/>
       <c r="E3" s="42"/>
       <c r="F3" s="43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -2361,10 +2364,10 @@
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K5" s="10" t="s">
         <v>3</v>
@@ -2398,10 +2401,10 @@
         <v>10</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K6" s="10" t="s">
         <v>11</v>
@@ -2424,7 +2427,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>68</v>
@@ -2437,7 +2440,7 @@
         <v>518733994</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I7" s="21">
         <v>1315032</v>
@@ -2483,7 +2486,7 @@
       </c>
       <c r="G8" s="20"/>
       <c r="H8" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I8" s="21"/>
       <c r="J8" s="21"/>
@@ -2523,7 +2526,7 @@
       </c>
       <c r="G9" s="20"/>
       <c r="H9" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I9" s="21"/>
       <c r="J9" s="21"/>
@@ -2563,7 +2566,7 @@
       </c>
       <c r="G10" s="20"/>
       <c r="H10" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I10" s="21"/>
       <c r="J10" s="21"/>
@@ -2603,7 +2606,7 @@
       </c>
       <c r="G11" s="20"/>
       <c r="H11" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I11" s="21"/>
       <c r="J11" s="21"/>
@@ -2643,7 +2646,7 @@
       </c>
       <c r="G12" s="20"/>
       <c r="H12" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I12" s="21"/>
       <c r="J12" s="21"/>
@@ -2683,7 +2686,7 @@
       </c>
       <c r="G13" s="20"/>
       <c r="H13" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I13" s="21"/>
       <c r="J13" s="21"/>
@@ -2723,7 +2726,7 @@
       </c>
       <c r="G14" s="20"/>
       <c r="H14" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I14" s="36"/>
       <c r="J14" s="36"/>
@@ -2763,7 +2766,7 @@
       </c>
       <c r="G15" s="20"/>
       <c r="H15" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I15" s="21"/>
       <c r="J15" s="21"/>
@@ -2803,7 +2806,7 @@
       </c>
       <c r="G16" s="20"/>
       <c r="H16" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I16" s="21"/>
       <c r="J16" s="21"/>
@@ -2843,7 +2846,7 @@
       </c>
       <c r="G17" s="20"/>
       <c r="H17" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I17" s="21"/>
       <c r="J17" s="21"/>
@@ -2883,7 +2886,7 @@
       </c>
       <c r="G18" s="20"/>
       <c r="H18" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I18" s="21"/>
       <c r="J18" s="21"/>
@@ -2923,7 +2926,7 @@
       </c>
       <c r="G19" s="20"/>
       <c r="H19" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I19" s="21"/>
       <c r="J19" s="21"/>
@@ -2963,7 +2966,7 @@
       </c>
       <c r="G20" s="20"/>
       <c r="H20" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I20" s="21"/>
       <c r="J20" s="21"/>
@@ -3003,7 +3006,7 @@
       </c>
       <c r="G21" s="20"/>
       <c r="H21" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I21" s="21"/>
       <c r="J21" s="21"/>
@@ -3043,7 +3046,7 @@
       </c>
       <c r="G22" s="20"/>
       <c r="H22" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I22" s="21"/>
       <c r="J22" s="21"/>
@@ -3083,7 +3086,7 @@
       </c>
       <c r="G23" s="20"/>
       <c r="H23" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I23" s="21"/>
       <c r="J23" s="21"/>
@@ -3123,7 +3126,7 @@
       </c>
       <c r="G24" s="20"/>
       <c r="H24" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I24" s="21"/>
       <c r="J24" s="21"/>
@@ -3163,7 +3166,7 @@
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I25" s="21"/>
       <c r="J25" s="21"/>
@@ -3203,7 +3206,7 @@
       </c>
       <c r="G26" s="20"/>
       <c r="H26" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I26" s="21"/>
       <c r="J26" s="21"/>
@@ -3243,7 +3246,7 @@
       </c>
       <c r="G27" s="20"/>
       <c r="H27" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I27" s="21"/>
       <c r="J27" s="21"/>
@@ -3299,12 +3302,12 @@
     </row>
     <row r="30" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C30" s="41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D30" s="42"/>
       <c r="E30" s="42"/>
       <c r="F30" s="43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -3339,10 +3342,10 @@
       </c>
       <c r="H32" s="9"/>
       <c r="I32" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K32" s="10" t="s">
         <v>3</v>
@@ -3376,10 +3379,10 @@
         <v>10</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K33" s="10" t="s">
         <v>11</v>
@@ -3409,10 +3412,10 @@
         <v>70</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I34" s="20"/>
       <c r="J34" s="20"/>
@@ -3437,7 +3440,9 @@
       <c r="A35">
         <v>3</v>
       </c>
-      <c r="C35" s="19"/>
+      <c r="C35" s="19">
+        <v>46088</v>
+      </c>
       <c r="D35" s="20" t="s">
         <v>68</v>
       </c>
@@ -3445,24 +3450,28 @@
       <c r="F35" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G35" s="37"/>
+      <c r="G35" s="37" t="s">
+        <v>87</v>
+      </c>
       <c r="H35" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I35" s="20"/>
       <c r="J35" s="20"/>
-      <c r="K35" s="21"/>
+      <c r="K35" s="21">
+        <v>203796</v>
+      </c>
       <c r="M35" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21835.285714285714</v>
       </c>
       <c r="N35" s="27">
         <f t="shared" ref="N35:N53" si="10">K35-M35</f>
-        <v>0</v>
+        <v>181960.71428571429</v>
       </c>
       <c r="O35" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1819.6071428571429</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -3479,7 +3488,7 @@
       </c>
       <c r="G36" s="37"/>
       <c r="H36" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I36" s="20"/>
       <c r="J36" s="20"/>
@@ -3511,7 +3520,7 @@
       </c>
       <c r="G37" s="37"/>
       <c r="H37" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I37" s="20"/>
       <c r="J37" s="20"/>
@@ -3543,7 +3552,7 @@
       </c>
       <c r="G38" s="37"/>
       <c r="H38" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I38" s="20"/>
       <c r="J38" s="20"/>
@@ -3575,7 +3584,7 @@
       </c>
       <c r="G39" s="37"/>
       <c r="H39" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I39" s="20"/>
       <c r="J39" s="20"/>
@@ -3607,7 +3616,7 @@
       </c>
       <c r="G40" s="37"/>
       <c r="H40" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I40" s="20"/>
       <c r="J40" s="20"/>
@@ -3639,7 +3648,7 @@
       </c>
       <c r="G41" s="37"/>
       <c r="H41" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I41" s="20"/>
       <c r="J41" s="20"/>
@@ -3671,7 +3680,7 @@
       </c>
       <c r="G42" s="37"/>
       <c r="H42" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I42" s="20"/>
       <c r="J42" s="20"/>
@@ -3703,7 +3712,7 @@
       </c>
       <c r="G43" s="37"/>
       <c r="H43" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I43" s="20"/>
       <c r="J43" s="20"/>
@@ -3735,7 +3744,7 @@
       </c>
       <c r="G44" s="37"/>
       <c r="H44" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I44" s="20"/>
       <c r="J44" s="20"/>
@@ -3767,7 +3776,7 @@
       </c>
       <c r="G45" s="37"/>
       <c r="H45" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I45" s="20"/>
       <c r="J45" s="20"/>
@@ -3799,7 +3808,7 @@
       </c>
       <c r="G46" s="37"/>
       <c r="H46" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I46" s="20"/>
       <c r="J46" s="20"/>
@@ -3831,7 +3840,7 @@
       </c>
       <c r="G47" s="37"/>
       <c r="H47" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I47" s="20"/>
       <c r="J47" s="20"/>
@@ -3863,7 +3872,7 @@
       </c>
       <c r="G48" s="37"/>
       <c r="H48" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I48" s="20"/>
       <c r="J48" s="20"/>
@@ -3895,7 +3904,7 @@
       </c>
       <c r="G49" s="37"/>
       <c r="H49" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I49" s="20"/>
       <c r="J49" s="20"/>
@@ -3927,7 +3936,7 @@
       </c>
       <c r="G50" s="37"/>
       <c r="H50" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I50" s="20"/>
       <c r="J50" s="20"/>
@@ -3959,7 +3968,7 @@
       </c>
       <c r="G51" s="37"/>
       <c r="H51" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I51" s="20"/>
       <c r="J51" s="20"/>
@@ -3991,7 +4000,7 @@
       </c>
       <c r="G52" s="37"/>
       <c r="H52" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I52" s="20"/>
       <c r="J52" s="20"/>
@@ -4023,7 +4032,7 @@
       </c>
       <c r="G53" s="37"/>
       <c r="H53" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I53" s="20"/>
       <c r="J53" s="20"/>
@@ -4055,7 +4064,7 @@
       </c>
       <c r="G54" s="37"/>
       <c r="H54" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I54" s="20"/>
       <c r="J54" s="20"/>
@@ -4067,7 +4076,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>197532</v>
+        <v>401328</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4075,15 +4084,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>21164.142857142855</v>
+        <v>42999.428571428565</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>176367.85714285716</v>
+        <v>358328.57142857148</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>1763.6785714285713</v>
+        <v>3583.2857142857142</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -4091,12 +4100,12 @@
     </row>
     <row r="57" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C57" s="41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D57" s="42"/>
       <c r="E57" s="42"/>
       <c r="F57" s="43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -4131,10 +4140,10 @@
       </c>
       <c r="H59" s="9"/>
       <c r="I59" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K59" s="10" t="s">
         <v>3</v>
@@ -4168,10 +4177,10 @@
         <v>10</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K60" s="10" t="s">
         <v>11</v>
@@ -4201,10 +4210,10 @@
         <v>70</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I61" s="20"/>
       <c r="J61" s="20"/>
@@ -4238,7 +4247,7 @@
       </c>
       <c r="G62" s="37"/>
       <c r="H62" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I62" s="20"/>
       <c r="J62" s="20"/>
@@ -4270,7 +4279,7 @@
       </c>
       <c r="G63" s="37"/>
       <c r="H63" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I63" s="20"/>
       <c r="J63" s="20"/>
@@ -4302,7 +4311,7 @@
       </c>
       <c r="G64" s="37"/>
       <c r="H64" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I64" s="20"/>
       <c r="J64" s="20"/>
@@ -4334,7 +4343,7 @@
       </c>
       <c r="G65" s="37"/>
       <c r="H65" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I65" s="20"/>
       <c r="J65" s="20"/>
@@ -4366,7 +4375,7 @@
       </c>
       <c r="G66" s="37"/>
       <c r="H66" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I66" s="20"/>
       <c r="J66" s="20"/>
@@ -4398,7 +4407,7 @@
       </c>
       <c r="G67" s="37"/>
       <c r="H67" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I67" s="20"/>
       <c r="J67" s="20"/>
@@ -4430,7 +4439,7 @@
       </c>
       <c r="G68" s="37"/>
       <c r="H68" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I68" s="20"/>
       <c r="J68" s="20"/>
@@ -4462,7 +4471,7 @@
       </c>
       <c r="G69" s="37"/>
       <c r="H69" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I69" s="20"/>
       <c r="J69" s="20"/>
@@ -4494,7 +4503,7 @@
       </c>
       <c r="G70" s="37"/>
       <c r="H70" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I70" s="20"/>
       <c r="J70" s="20"/>
@@ -4526,7 +4535,7 @@
       </c>
       <c r="G71" s="37"/>
       <c r="H71" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I71" s="20"/>
       <c r="J71" s="20"/>
@@ -4558,7 +4567,7 @@
       </c>
       <c r="G72" s="37"/>
       <c r="H72" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I72" s="20"/>
       <c r="J72" s="20"/>
@@ -4590,7 +4599,7 @@
       </c>
       <c r="G73" s="37"/>
       <c r="H73" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I73" s="20"/>
       <c r="J73" s="20"/>
@@ -4622,7 +4631,7 @@
       </c>
       <c r="G74" s="37"/>
       <c r="H74" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I74" s="20"/>
       <c r="J74" s="20"/>
@@ -4654,7 +4663,7 @@
       </c>
       <c r="G75" s="37"/>
       <c r="H75" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I75" s="20"/>
       <c r="J75" s="20"/>
@@ -4686,7 +4695,7 @@
       </c>
       <c r="G76" s="37"/>
       <c r="H76" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I76" s="20"/>
       <c r="J76" s="20"/>
@@ -4718,7 +4727,7 @@
       </c>
       <c r="G77" s="37"/>
       <c r="H77" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I77" s="20"/>
       <c r="J77" s="20"/>
@@ -4750,7 +4759,7 @@
       </c>
       <c r="G78" s="37"/>
       <c r="H78" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I78" s="20"/>
       <c r="J78" s="20"/>
@@ -4782,7 +4791,7 @@
       </c>
       <c r="G79" s="37"/>
       <c r="H79" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I79" s="20"/>
       <c r="J79" s="20"/>
@@ -4814,7 +4823,7 @@
       </c>
       <c r="G80" s="37"/>
       <c r="H80" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I80" s="20"/>
       <c r="J80" s="20"/>
@@ -4846,7 +4855,7 @@
       </c>
       <c r="G81" s="37"/>
       <c r="H81" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I81" s="20"/>
       <c r="J81" s="20"/>
@@ -4879,12 +4888,12 @@
     </row>
     <row r="84" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C84" s="41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D84" s="42"/>
       <c r="E84" s="42"/>
       <c r="F84" s="43" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
@@ -4919,10 +4928,10 @@
       </c>
       <c r="H86" s="9"/>
       <c r="I86" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J86" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M86" s="10" t="s">
         <v>3</v>
@@ -4956,13 +4965,13 @@
         <v>10</v>
       </c>
       <c r="I87" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J87" s="9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K87" s="46" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M87" s="10" t="s">
         <v>11</v>
@@ -4982,7 +4991,7 @@
         <v>2</v>
       </c>
       <c r="C88" s="19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D88" s="20" t="s">
         <v>68</v>
@@ -4992,10 +5001,10 @@
         <v>70</v>
       </c>
       <c r="G88" s="37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H88" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I88" s="20"/>
       <c r="J88" s="20"/>
@@ -5033,7 +5042,7 @@
       </c>
       <c r="G89" s="37"/>
       <c r="H89" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I89" s="20"/>
       <c r="J89" s="20"/>
@@ -5067,7 +5076,7 @@
       </c>
       <c r="G90" s="37"/>
       <c r="H90" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I90" s="20"/>
       <c r="J90" s="20"/>
@@ -5101,7 +5110,7 @@
       </c>
       <c r="G91" s="37"/>
       <c r="H91" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I91" s="20"/>
       <c r="J91" s="20"/>
@@ -5135,7 +5144,7 @@
       </c>
       <c r="G92" s="37"/>
       <c r="H92" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I92" s="20"/>
       <c r="J92" s="20"/>
@@ -5169,7 +5178,7 @@
       </c>
       <c r="G93" s="37"/>
       <c r="H93" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I93" s="20"/>
       <c r="J93" s="20"/>
@@ -5203,7 +5212,7 @@
       </c>
       <c r="G94" s="37"/>
       <c r="H94" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I94" s="20"/>
       <c r="J94" s="20"/>
@@ -5237,7 +5246,7 @@
       </c>
       <c r="G95" s="37"/>
       <c r="H95" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I95" s="20"/>
       <c r="J95" s="20"/>
@@ -5271,7 +5280,7 @@
       </c>
       <c r="G96" s="37"/>
       <c r="H96" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I96" s="20"/>
       <c r="J96" s="20"/>
@@ -5305,7 +5314,7 @@
       </c>
       <c r="G97" s="37"/>
       <c r="H97" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I97" s="20"/>
       <c r="J97" s="20"/>
@@ -5339,7 +5348,7 @@
       </c>
       <c r="G98" s="37"/>
       <c r="H98" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I98" s="20"/>
       <c r="J98" s="20"/>
@@ -5373,7 +5382,7 @@
       </c>
       <c r="G99" s="37"/>
       <c r="H99" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I99" s="20"/>
       <c r="J99" s="20"/>
@@ -5407,7 +5416,7 @@
       </c>
       <c r="G100" s="37"/>
       <c r="H100" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I100" s="20"/>
       <c r="J100" s="20"/>
@@ -5441,7 +5450,7 @@
       </c>
       <c r="G101" s="37"/>
       <c r="H101" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I101" s="20"/>
       <c r="J101" s="20"/>
@@ -5475,7 +5484,7 @@
       </c>
       <c r="G102" s="37"/>
       <c r="H102" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I102" s="20"/>
       <c r="J102" s="20"/>
@@ -5509,7 +5518,7 @@
       </c>
       <c r="G103" s="37"/>
       <c r="H103" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I103" s="20"/>
       <c r="J103" s="20"/>
@@ -5543,7 +5552,7 @@
       </c>
       <c r="G104" s="37"/>
       <c r="H104" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I104" s="20"/>
       <c r="J104" s="20"/>
@@ -5577,7 +5586,7 @@
       </c>
       <c r="G105" s="37"/>
       <c r="H105" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I105" s="20"/>
       <c r="J105" s="20"/>
@@ -5611,7 +5620,7 @@
       </c>
       <c r="G106" s="37"/>
       <c r="H106" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I106" s="20"/>
       <c r="J106" s="20"/>
@@ -5645,7 +5654,7 @@
       </c>
       <c r="G107" s="37"/>
       <c r="H107" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I107" s="20"/>
       <c r="J107" s="20"/>
@@ -5679,7 +5688,7 @@
       </c>
       <c r="G108" s="37"/>
       <c r="H108" s="20" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="I108" s="20"/>
       <c r="J108" s="20"/>

--- a/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5112D3EC-FBC8-4859-A96B-082573D3CAB5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084F294B-21EC-448A-B558-59D1B5E140F3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="90">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -300,6 +300,9 @@
   </si>
   <si>
     <t>166-562-025-0005</t>
+  </si>
+  <si>
+    <t>R03</t>
   </si>
 </sst>
 </file>
@@ -3478,7 +3481,9 @@
       <c r="A36">
         <v>4</v>
       </c>
-      <c r="C36" s="19"/>
+      <c r="C36" s="19">
+        <v>46210</v>
+      </c>
       <c r="D36" s="20" t="s">
         <v>68</v>
       </c>
@@ -3486,24 +3491,28 @@
       <c r="F36" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G36" s="37"/>
+      <c r="G36" s="37" t="s">
+        <v>89</v>
+      </c>
       <c r="H36" s="20" t="s">
         <v>88</v>
       </c>
       <c r="I36" s="20"/>
       <c r="J36" s="20"/>
-      <c r="K36" s="21"/>
+      <c r="K36" s="21">
+        <v>203796</v>
+      </c>
       <c r="M36" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21835.285714285714</v>
       </c>
       <c r="N36" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>181960.71428571429</v>
       </c>
       <c r="O36" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1819.6071428571429</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
@@ -4076,7 +4085,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>401328</v>
+        <v>605124</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4084,15 +4093,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>42999.428571428565</v>
+        <v>64834.714285714275</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>358328.57142857148</v>
+        <v>540289.2857142858</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>3583.2857142857142</v>
+        <v>5402.8928571428569</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">

--- a/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084F294B-21EC-448A-B558-59D1B5E140F3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B67857B-08DF-41B6-B54C-624152168171}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="91">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -303,6 +303,9 @@
   </si>
   <si>
     <t>R03</t>
+  </si>
+  <si>
+    <t>R04</t>
   </si>
 </sst>
 </file>
@@ -3519,7 +3522,9 @@
       <c r="A37">
         <v>5</v>
       </c>
-      <c r="C37" s="19"/>
+      <c r="C37" s="19">
+        <v>46272</v>
+      </c>
       <c r="D37" s="20" t="s">
         <v>68</v>
       </c>
@@ -3527,7 +3532,9 @@
       <c r="F37" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G37" s="37"/>
+      <c r="G37" s="37" t="s">
+        <v>90</v>
+      </c>
       <c r="H37" s="20" t="s">
         <v>88</v>
       </c>

--- a/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B67857B-08DF-41B6-B54C-624152168171}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321C45C9-3E65-49D9-A0D5-87546F20188C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3540,18 +3540,20 @@
       </c>
       <c r="I37" s="20"/>
       <c r="J37" s="20"/>
-      <c r="K37" s="21"/>
+      <c r="K37" s="21">
+        <v>198036</v>
+      </c>
       <c r="M37" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21218.142857142855</v>
       </c>
       <c r="N37" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>176817.85714285716</v>
       </c>
       <c r="O37" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1768.1785714285713</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -4092,7 +4094,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>605124</v>
+        <v>803160</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4100,15 +4102,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>64834.714285714275</v>
+        <v>86052.85714285713</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>540289.2857142858</v>
+        <v>717107.14285714296</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>5402.8928571428569</v>
+        <v>7171.0714285714284</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">

--- a/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321C45C9-3E65-49D9-A0D5-87546F20188C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E46CEACC-13A5-488E-A59D-73CA972DB475}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E46CEACC-13A5-488E-A59D-73CA972DB475}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CFB564F-FBA2-4A4D-84AC-BFC725CC13BE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3275,12 +3275,8 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G28"/>
-      <c r="I28" s="44">
-        <v>12457285</v>
-      </c>
-      <c r="J28" s="44">
-        <v>776843.10000000009</v>
-      </c>
+      <c r="I28" s="44"/>
+      <c r="J28" s="44"/>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
         <v>1042000.3200000001</v>

--- a/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CFB564F-FBA2-4A4D-84AC-BFC725CC13BE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45FCBA56-82DD-4674-B443-6EE3EBC81D98}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="93">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -306,6 +306,12 @@
   </si>
   <si>
     <t>R04</t>
+  </si>
+  <si>
+    <t>07/16/2026</t>
+  </si>
+  <si>
+    <t>R05</t>
   </si>
 </sst>
 </file>
@@ -2433,7 +2439,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>68</v>
@@ -2443,32 +2449,32 @@
         <v>70</v>
       </c>
       <c r="G7" s="20">
-        <v>518733994</v>
+        <v>518825276</v>
       </c>
       <c r="H7" s="20" t="s">
         <v>88</v>
       </c>
       <c r="I7" s="21">
-        <v>1315032</v>
+        <v>1376614</v>
       </c>
       <c r="J7" s="21">
-        <v>273031.67999999999</v>
+        <v>109178.29</v>
       </c>
       <c r="K7" s="21">
         <f>I7-J7</f>
-        <v>1042000.3200000001</v>
+        <v>1267435.71</v>
       </c>
       <c r="M7" s="21">
         <f>O7*12</f>
-        <v>111642.89142857144</v>
+        <v>135796.6832142857</v>
       </c>
       <c r="N7" s="27">
         <f>K7-M7</f>
-        <v>930357.42857142864</v>
+        <v>1131639.0267857143</v>
       </c>
       <c r="O7" s="33">
         <f>K7/112</f>
-        <v>9303.5742857142868</v>
+        <v>11316.390267857143</v>
       </c>
       <c r="P7" s="26"/>
       <c r="Q7" s="26"/>
@@ -3279,7 +3285,7 @@
       <c r="J28" s="44"/>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>1042000.3200000001</v>
+        <v>1267435.71</v>
       </c>
       <c r="L28" s="44">
         <f ca="1">SUM(L7:L31)</f>
@@ -3287,15 +3293,15 @@
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>111642.89142857144</v>
+        <v>135796.6832142857</v>
       </c>
       <c r="N28" s="44">
         <f>SUM(N7:N27)</f>
-        <v>930357.42857142864</v>
+        <v>1131639.0267857143</v>
       </c>
       <c r="O28" s="44">
         <f>SUM(O7:O27)</f>
-        <v>9303.5742857142868</v>
+        <v>11316.390267857143</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3556,7 +3562,9 @@
       <c r="A38">
         <v>6</v>
       </c>
-      <c r="C38" s="19"/>
+      <c r="C38" s="19" t="s">
+        <v>91</v>
+      </c>
       <c r="D38" s="20" t="s">
         <v>68</v>
       </c>
@@ -3564,24 +3572,29 @@
       <c r="F38" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G38" s="37"/>
+      <c r="G38" s="37" t="s">
+        <v>92</v>
+      </c>
       <c r="H38" s="20" t="s">
         <v>88</v>
       </c>
       <c r="I38" s="20"/>
       <c r="J38" s="20"/>
-      <c r="K38" s="21"/>
+      <c r="K38" s="21">
+        <f>11988+15120+155844+9072</f>
+        <v>192024</v>
+      </c>
       <c r="M38" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>20574</v>
       </c>
       <c r="N38" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>171450</v>
       </c>
       <c r="O38" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1714.5</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
@@ -4090,7 +4103,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>803160</v>
+        <v>995184</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4098,15 +4111,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>86052.85714285713</v>
+        <v>106626.85714285713</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>717107.14285714296</v>
+        <v>888557.14285714296</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>7171.0714285714284</v>
+        <v>8885.5714285714275</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">

--- a/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45FCBA56-82DD-4674-B443-6EE3EBC81D98}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18904FBD-7D84-4A9D-A73E-4D2E122CC443}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="95">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -312,6 +312,12 @@
   </si>
   <si>
     <t>R05</t>
+  </si>
+  <si>
+    <t>07/17/2026</t>
+  </si>
+  <si>
+    <t>R06</t>
   </si>
 </sst>
 </file>
@@ -2488,7 +2494,9 @@
         <f>B7+1</f>
         <v>2</v>
       </c>
-      <c r="C8" s="19"/>
+      <c r="C8" s="19" t="s">
+        <v>93</v>
+      </c>
       <c r="D8" s="20" t="s">
         <v>68</v>
       </c>
@@ -2496,27 +2504,33 @@
       <c r="F8" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G8" s="20"/>
+      <c r="G8" s="20">
+        <v>518829090</v>
+      </c>
       <c r="H8" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="I8" s="21"/>
-      <c r="J8" s="21"/>
+      <c r="I8" s="21">
+        <v>1354770</v>
+      </c>
+      <c r="J8" s="21">
+        <v>72448.81</v>
+      </c>
       <c r="K8" s="21">
         <f t="shared" ref="K8:K27" si="0">I8-J8</f>
-        <v>0</v>
+        <v>1282321.19</v>
       </c>
       <c r="M8" s="21">
         <f>O8*12</f>
-        <v>0</v>
+        <v>137391.55607142858</v>
       </c>
       <c r="N8" s="27">
         <f>K8-M8</f>
-        <v>0</v>
+        <v>1144929.6339285714</v>
       </c>
       <c r="O8" s="33">
         <f t="shared" ref="O8:O26" si="1">K8/112</f>
-        <v>0</v>
+        <v>11449.296339285715</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -3285,7 +3299,7 @@
       <c r="J28" s="44"/>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>1267435.71</v>
+        <v>2549756.9</v>
       </c>
       <c r="L28" s="44">
         <f ca="1">SUM(L7:L31)</f>
@@ -3293,15 +3307,15 @@
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>135796.6832142857</v>
+        <v>273188.23928571428</v>
       </c>
       <c r="N28" s="44">
         <f>SUM(N7:N27)</f>
-        <v>1131639.0267857143</v>
+        <v>2276568.6607142854</v>
       </c>
       <c r="O28" s="44">
         <f>SUM(O7:O27)</f>
-        <v>11316.390267857143</v>
+        <v>22765.686607142859</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3601,7 +3615,9 @@
       <c r="A39">
         <v>7</v>
       </c>
-      <c r="C39" s="19"/>
+      <c r="C39" s="19" t="s">
+        <v>93</v>
+      </c>
       <c r="D39" s="20" t="s">
         <v>68</v>
       </c>
@@ -3609,24 +3625,29 @@
       <c r="F39" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G39" s="37"/>
+      <c r="G39" s="37" t="s">
+        <v>94</v>
+      </c>
       <c r="H39" s="20" t="s">
         <v>88</v>
       </c>
       <c r="I39" s="20"/>
       <c r="J39" s="20"/>
-      <c r="K39" s="21"/>
+      <c r="K39" s="21">
+        <f>23976+179820</f>
+        <v>203796</v>
+      </c>
       <c r="M39" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21835.285714285714</v>
       </c>
       <c r="N39" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>181960.71428571429</v>
       </c>
       <c r="O39" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1819.6071428571429</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
@@ -4103,7 +4124,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>995184</v>
+        <v>1198980</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4111,15 +4132,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>106626.85714285713</v>
+        <v>128462.14285714284</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>888557.14285714296</v>
+        <v>1070517.8571428573</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>8885.5714285714275</v>
+        <v>10705.178571428571</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">

--- a/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18904FBD-7D84-4A9D-A73E-4D2E122CC443}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025B067F-76E4-4C1E-A4A7-FF37223E1358}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="99">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -318,6 +318,18 @@
   </si>
   <si>
     <t>R06</t>
+  </si>
+  <si>
+    <t>07/18/2026</t>
+  </si>
+  <si>
+    <t>R07</t>
+  </si>
+  <si>
+    <t>07/20/2026</t>
+  </si>
+  <si>
+    <t>R08</t>
   </si>
 </sst>
 </file>
@@ -3654,7 +3666,9 @@
       <c r="A40">
         <v>8</v>
       </c>
-      <c r="C40" s="19"/>
+      <c r="C40" s="19" t="s">
+        <v>95</v>
+      </c>
       <c r="D40" s="20" t="s">
         <v>68</v>
       </c>
@@ -3662,31 +3676,38 @@
       <c r="F40" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G40" s="37"/>
+      <c r="G40" s="37" t="s">
+        <v>96</v>
+      </c>
       <c r="H40" s="20" t="s">
         <v>88</v>
       </c>
       <c r="I40" s="20"/>
       <c r="J40" s="20"/>
-      <c r="K40" s="21"/>
+      <c r="K40" s="21">
+        <f>11988+10656+179820</f>
+        <v>202464</v>
+      </c>
       <c r="M40" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21692.571428571428</v>
       </c>
       <c r="N40" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>180771.42857142858</v>
       </c>
       <c r="O40" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1807.7142857142858</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>9</v>
       </c>
-      <c r="C41" s="19"/>
+      <c r="C41" s="19" t="s">
+        <v>97</v>
+      </c>
       <c r="D41" s="20" t="s">
         <v>68</v>
       </c>
@@ -3694,24 +3715,29 @@
       <c r="F41" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G41" s="37"/>
+      <c r="G41" s="37" t="s">
+        <v>98</v>
+      </c>
       <c r="H41" s="20" t="s">
         <v>88</v>
       </c>
       <c r="I41" s="20"/>
       <c r="J41" s="20"/>
-      <c r="K41" s="21"/>
+      <c r="K41" s="21">
+        <f>11988+167832</f>
+        <v>179820</v>
+      </c>
       <c r="M41" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>19266.428571428572</v>
       </c>
       <c r="N41" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>160553.57142857142</v>
       </c>
       <c r="O41" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1605.5357142857142</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -4124,7 +4150,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>1198980</v>
+        <v>1581264</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4132,15 +4158,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>128462.14285714284</v>
+        <v>169421.14285714284</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>1070517.8571428573</v>
+        <v>1411842.8571428573</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>10705.178571428571</v>
+        <v>14118.428571428571</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -4247,8 +4273,8 @@
       <c r="A61">
         <v>2</v>
       </c>
-      <c r="C61" s="19">
-        <v>46028</v>
+      <c r="C61" s="19" t="s">
+        <v>97</v>
       </c>
       <c r="D61" s="20" t="s">
         <v>68</v>
@@ -4258,7 +4284,7 @@
         <v>70</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="H61" s="20" t="s">
         <v>88</v>
@@ -4266,19 +4292,20 @@
       <c r="I61" s="20"/>
       <c r="J61" s="20"/>
       <c r="K61" s="21">
-        <v>33804</v>
+        <f>78*144</f>
+        <v>11232</v>
       </c>
       <c r="M61" s="21">
         <f t="shared" ref="M61:M80" si="11">O61*12</f>
-        <v>3621.8571428571427</v>
+        <v>1203.4285714285716</v>
       </c>
       <c r="N61" s="27">
         <f>K61-M61</f>
-        <v>30182.142857142859</v>
+        <v>10028.571428571428</v>
       </c>
       <c r="O61" s="33">
         <f t="shared" ref="O61:O80" si="12">K61/112</f>
-        <v>301.82142857142856</v>
+        <v>100.28571428571429</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
@@ -4915,7 +4942,7 @@
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K82" s="44">
         <f>SUM(K61:K81)</f>
-        <v>33804</v>
+        <v>11232</v>
       </c>
       <c r="L82" s="44">
         <f ca="1">SUM(L61:L85)</f>
@@ -4923,15 +4950,15 @@
       </c>
       <c r="M82" s="44">
         <f>SUM(M61:M81)</f>
-        <v>3621.8571428571427</v>
+        <v>1203.4285714285716</v>
       </c>
       <c r="N82" s="44">
         <f>SUM(N61:N81)</f>
-        <v>30182.142857142859</v>
+        <v>10028.571428571428</v>
       </c>
       <c r="O82" s="45">
         <f>SUM(O61:O81)</f>
-        <v>301.82142857142856</v>
+        <v>100.28571428571429</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">

--- a/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025B067F-76E4-4C1E-A4A7-FF37223E1358}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86B002D-D8A7-493C-9057-E6F83F802C66}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="101">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -330,6 +330,12 @@
   </si>
   <si>
     <t>R08</t>
+  </si>
+  <si>
+    <t>07/21/2026</t>
+  </si>
+  <si>
+    <t>R09</t>
   </si>
 </sst>
 </file>
@@ -2554,7 +2560,9 @@
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="C9" s="19"/>
+      <c r="C9" s="19" t="s">
+        <v>99</v>
+      </c>
       <c r="D9" s="20" t="s">
         <v>68</v>
       </c>
@@ -2562,27 +2570,34 @@
       <c r="F9" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G9" s="20"/>
+      <c r="G9" s="20">
+        <v>518839710</v>
+      </c>
       <c r="H9" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
+      <c r="I9" s="21">
+        <f>1397196</f>
+        <v>1397196</v>
+      </c>
+      <c r="J9" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K9" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1336350.96</v>
       </c>
       <c r="M9" s="21">
         <f t="shared" ref="M9:M26" si="3">O9*12</f>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="N9" s="27">
         <f t="shared" ref="N9:N26" si="4">K9-M9</f>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="O9" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3311,7 +3326,7 @@
       <c r="J28" s="44"/>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>2549756.9</v>
+        <v>3886107.86</v>
       </c>
       <c r="L28" s="44">
         <f ca="1">SUM(L7:L31)</f>
@@ -3319,15 +3334,15 @@
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>273188.23928571428</v>
+        <v>416368.69928571431</v>
       </c>
       <c r="N28" s="44">
         <f>SUM(N7:N27)</f>
-        <v>2276568.6607142854</v>
+        <v>3469739.1607142854</v>
       </c>
       <c r="O28" s="44">
         <f>SUM(O7:O27)</f>
-        <v>22765.686607142859</v>
+        <v>34697.391607142861</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3744,7 +3759,9 @@
       <c r="A42">
         <v>10</v>
       </c>
-      <c r="C42" s="19"/>
+      <c r="C42" s="19" t="s">
+        <v>99</v>
+      </c>
       <c r="D42" s="20" t="s">
         <v>68</v>
       </c>
@@ -3752,24 +3769,29 @@
       <c r="F42" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G42" s="37"/>
+      <c r="G42" s="37" t="s">
+        <v>100</v>
+      </c>
       <c r="H42" s="20" t="s">
         <v>88</v>
       </c>
       <c r="I42" s="20"/>
       <c r="J42" s="20"/>
-      <c r="K42" s="21"/>
+      <c r="K42" s="21">
+        <f>23976+143856+18144</f>
+        <v>185976</v>
+      </c>
       <c r="M42" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>19926</v>
       </c>
       <c r="N42" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>166050</v>
       </c>
       <c r="O42" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1660.5</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -4150,7 +4172,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>1581264</v>
+        <v>1767240</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4158,15 +4180,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>169421.14285714284</v>
+        <v>189347.14285714284</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>1411842.8571428573</v>
+        <v>1577892.8571428573</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>14118.428571428571</v>
+        <v>15778.928571428571</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -4312,7 +4334,9 @@
       <c r="A62">
         <v>3</v>
       </c>
-      <c r="C62" s="19"/>
+      <c r="C62" s="19" t="s">
+        <v>99</v>
+      </c>
       <c r="D62" s="20" t="s">
         <v>68</v>
       </c>
@@ -4320,24 +4344,28 @@
       <c r="F62" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G62" s="37"/>
+      <c r="G62" s="37" t="s">
+        <v>100</v>
+      </c>
       <c r="H62" s="20" t="s">
         <v>88</v>
       </c>
       <c r="I62" s="20"/>
       <c r="J62" s="20"/>
-      <c r="K62" s="21"/>
+      <c r="K62" s="21">
+        <v>5670</v>
+      </c>
       <c r="M62" s="21">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>607.5</v>
       </c>
       <c r="N62" s="27">
         <f t="shared" ref="N62:N80" si="13">K62-M62</f>
-        <v>0</v>
+        <v>5062.5</v>
       </c>
       <c r="O62" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>50.625</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
@@ -4942,7 +4970,7 @@
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K82" s="44">
         <f>SUM(K61:K81)</f>
-        <v>11232</v>
+        <v>16902</v>
       </c>
       <c r="L82" s="44">
         <f ca="1">SUM(L61:L85)</f>
@@ -4950,15 +4978,15 @@
       </c>
       <c r="M82" s="44">
         <f>SUM(M61:M81)</f>
-        <v>1203.4285714285716</v>
+        <v>1810.9285714285716</v>
       </c>
       <c r="N82" s="44">
         <f>SUM(N61:N81)</f>
-        <v>10028.571428571428</v>
+        <v>15091.071428571428</v>
       </c>
       <c r="O82" s="45">
         <f>SUM(O61:O81)</f>
-        <v>100.28571428571429</v>
+        <v>150.91071428571428</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">

--- a/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F86B002D-D8A7-493C-9057-E6F83F802C66}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354088D0-E359-4916-ACBA-0E007264E820}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="103">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -336,6 +336,12 @@
   </si>
   <si>
     <t>R09</t>
+  </si>
+  <si>
+    <t>07/22/2026</t>
+  </si>
+  <si>
+    <t>R10</t>
   </si>
 </sst>
 </file>
@@ -2609,7 +2615,9 @@
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="C10" s="19"/>
+      <c r="C10" s="19" t="s">
+        <v>101</v>
+      </c>
       <c r="D10" s="20" t="s">
         <v>68</v>
       </c>
@@ -2617,27 +2625,33 @@
       <c r="F10" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G10" s="20"/>
+      <c r="G10" s="20">
+        <v>518843320</v>
+      </c>
       <c r="H10" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21"/>
+      <c r="I10" s="21">
+        <v>1397196</v>
+      </c>
+      <c r="J10" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K10" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1336350.96</v>
       </c>
       <c r="M10" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="N10" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="O10" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -3326,7 +3340,7 @@
       <c r="J28" s="44"/>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>3886107.86</v>
+        <v>5222458.82</v>
       </c>
       <c r="L28" s="44">
         <f ca="1">SUM(L7:L31)</f>
@@ -3334,15 +3348,15 @@
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>416368.69928571431</v>
+        <v>559549.15928571427</v>
       </c>
       <c r="N28" s="44">
         <f>SUM(N7:N27)</f>
-        <v>3469739.1607142854</v>
+        <v>4662909.6607142854</v>
       </c>
       <c r="O28" s="44">
         <f>SUM(O7:O27)</f>
-        <v>34697.391607142861</v>
+        <v>46629.096607142863</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3798,7 +3812,9 @@
       <c r="A43">
         <v>11</v>
       </c>
-      <c r="C43" s="19"/>
+      <c r="C43" s="19" t="s">
+        <v>101</v>
+      </c>
       <c r="D43" s="20" t="s">
         <v>68</v>
       </c>
@@ -3806,24 +3822,29 @@
       <c r="F43" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G43" s="37"/>
+      <c r="G43" s="37" t="s">
+        <v>102</v>
+      </c>
       <c r="H43" s="20" t="s">
         <v>88</v>
       </c>
       <c r="I43" s="20"/>
       <c r="J43" s="20"/>
-      <c r="K43" s="21"/>
+      <c r="K43" s="21">
+        <f>23976+10656+155844+9072</f>
+        <v>199548</v>
+      </c>
       <c r="M43" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21380.142857142855</v>
       </c>
       <c r="N43" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>178167.85714285716</v>
       </c>
       <c r="O43" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1781.6785714285713</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -4172,7 +4193,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>1767240</v>
+        <v>1966788</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4180,15 +4201,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>189347.14285714284</v>
+        <v>210727.28571428568</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>1577892.8571428573</v>
+        <v>1756060.7142857146</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>15778.928571428571</v>
+        <v>17560.607142857141</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">

--- a/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354088D0-E359-4916-ACBA-0E007264E820}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FBB139D-DC71-4BA7-929F-80F0DED34D1B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="105">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -342,6 +342,12 @@
   </si>
   <si>
     <t>R10</t>
+  </si>
+  <si>
+    <t>07/23/2026</t>
+  </si>
+  <si>
+    <t>R11</t>
   </si>
 </sst>
 </file>
@@ -2663,7 +2669,9 @@
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="C11" s="19"/>
+      <c r="C11" s="19" t="s">
+        <v>103</v>
+      </c>
       <c r="D11" s="20" t="s">
         <v>68</v>
       </c>
@@ -2671,27 +2679,33 @@
       <c r="F11" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G11" s="20"/>
+      <c r="G11" s="20">
+        <v>518846972</v>
+      </c>
       <c r="H11" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21"/>
+      <c r="I11" s="21">
+        <v>1397196</v>
+      </c>
+      <c r="J11" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K11" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1336350.96</v>
       </c>
       <c r="M11" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="N11" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="O11" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -3340,7 +3354,7 @@
       <c r="J28" s="44"/>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>5222458.82</v>
+        <v>6558809.7800000003</v>
       </c>
       <c r="L28" s="44">
         <f ca="1">SUM(L7:L31)</f>
@@ -3348,15 +3362,15 @@
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>559549.15928571427</v>
+        <v>702729.61928571423</v>
       </c>
       <c r="N28" s="44">
         <f>SUM(N7:N27)</f>
-        <v>4662909.6607142854</v>
+        <v>5856080.1607142854</v>
       </c>
       <c r="O28" s="44">
         <f>SUM(O7:O27)</f>
-        <v>46629.096607142863</v>
+        <v>58560.801607142865</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3851,7 +3865,9 @@
       <c r="A44">
         <v>12</v>
       </c>
-      <c r="C44" s="19"/>
+      <c r="C44" s="19" t="s">
+        <v>103</v>
+      </c>
       <c r="D44" s="20" t="s">
         <v>68</v>
       </c>
@@ -3859,24 +3875,29 @@
       <c r="F44" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G44" s="37"/>
+      <c r="G44" s="37" t="s">
+        <v>104</v>
+      </c>
       <c r="H44" s="20" t="s">
         <v>88</v>
       </c>
       <c r="I44" s="20"/>
       <c r="J44" s="20"/>
-      <c r="K44" s="21"/>
+      <c r="K44" s="21">
+        <f>11988+71928+5292+18144+8064</f>
+        <v>115416</v>
+      </c>
       <c r="M44" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>12366</v>
       </c>
       <c r="N44" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>103050</v>
       </c>
       <c r="O44" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1030.5</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
@@ -4193,7 +4214,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>1966788</v>
+        <v>2082204</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4201,15 +4222,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>210727.28571428568</v>
+        <v>223093.28571428568</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>1756060.7142857146</v>
+        <v>1859110.7142857146</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>17560.607142857141</v>
+        <v>18591.107142857141</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -4393,7 +4414,9 @@
       <c r="A63">
         <v>4</v>
       </c>
-      <c r="C63" s="19"/>
+      <c r="C63" s="19" t="s">
+        <v>103</v>
+      </c>
       <c r="D63" s="20" t="s">
         <v>68</v>
       </c>
@@ -4401,24 +4424,28 @@
       <c r="F63" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G63" s="37"/>
+      <c r="G63" s="37" t="s">
+        <v>104</v>
+      </c>
       <c r="H63" s="20" t="s">
         <v>88</v>
       </c>
       <c r="I63" s="20"/>
       <c r="J63" s="20"/>
-      <c r="K63" s="21"/>
+      <c r="K63" s="21">
+        <v>5616</v>
+      </c>
       <c r="M63" s="21">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>601.71428571428578</v>
       </c>
       <c r="N63" s="27">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>5014.2857142857138</v>
       </c>
       <c r="O63" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>50.142857142857146</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
@@ -4991,7 +5018,7 @@
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K82" s="44">
         <f>SUM(K61:K81)</f>
-        <v>16902</v>
+        <v>22518</v>
       </c>
       <c r="L82" s="44">
         <f ca="1">SUM(L61:L85)</f>
@@ -4999,15 +5026,15 @@
       </c>
       <c r="M82" s="44">
         <f>SUM(M61:M81)</f>
-        <v>1810.9285714285716</v>
+        <v>2412.6428571428573</v>
       </c>
       <c r="N82" s="44">
         <f>SUM(N61:N81)</f>
-        <v>15091.071428571428</v>
+        <v>20105.357142857141</v>
       </c>
       <c r="O82" s="45">
         <f>SUM(O61:O81)</f>
-        <v>150.91071428571428</v>
+        <v>201.05357142857142</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">

--- a/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FBB139D-DC71-4BA7-929F-80F0DED34D1B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FF3897-EB66-44C3-ABD3-3E266C228C25}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="107">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -348,6 +348,12 @@
   </si>
   <si>
     <t>R11</t>
+  </si>
+  <si>
+    <t>07/24/2026</t>
+  </si>
+  <si>
+    <t>R12</t>
   </si>
 </sst>
 </file>
@@ -2717,7 +2723,9 @@
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="C12" s="19"/>
+      <c r="C12" s="19" t="s">
+        <v>105</v>
+      </c>
       <c r="D12" s="20" t="s">
         <v>68</v>
       </c>
@@ -2725,27 +2733,33 @@
       <c r="F12" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G12" s="20"/>
+      <c r="G12" s="20">
+        <v>518850942</v>
+      </c>
       <c r="H12" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
+      <c r="I12" s="21">
+        <v>1397196</v>
+      </c>
+      <c r="J12" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K12" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1336350.96</v>
       </c>
       <c r="M12" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="N12" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="O12" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -2757,7 +2771,9 @@
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="C13" s="19"/>
+      <c r="C13" s="19" t="s">
+        <v>105</v>
+      </c>
       <c r="D13" s="20" t="s">
         <v>68</v>
       </c>
@@ -2765,27 +2781,33 @@
       <c r="F13" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G13" s="20"/>
+      <c r="G13" s="20">
+        <v>518851356</v>
+      </c>
       <c r="H13" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
+      <c r="I13" s="21">
+        <v>1397196</v>
+      </c>
+      <c r="J13" s="21">
+        <v>60845.04</v>
+      </c>
       <c r="K13" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1336350.96</v>
       </c>
       <c r="M13" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>143180.46</v>
       </c>
       <c r="N13" s="27">
         <f>K13-M13</f>
-        <v>0</v>
+        <v>1193170.5</v>
       </c>
       <c r="O13" s="33">
         <f>K13/112</f>
-        <v>0</v>
+        <v>11931.705</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -3354,7 +3376,7 @@
       <c r="J28" s="44"/>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>6558809.7800000003</v>
+        <v>9231511.6999999993</v>
       </c>
       <c r="L28" s="44">
         <f ca="1">SUM(L7:L31)</f>
@@ -3362,15 +3384,15 @@
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>702729.61928571423</v>
+        <v>989090.53928571416</v>
       </c>
       <c r="N28" s="44">
         <f>SUM(N7:N27)</f>
-        <v>5856080.1607142854</v>
+        <v>8242421.1607142854</v>
       </c>
       <c r="O28" s="44">
         <f>SUM(O7:O27)</f>
-        <v>58560.801607142865</v>
+        <v>82424.211607142861</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3904,7 +3926,9 @@
       <c r="A45">
         <v>13</v>
       </c>
-      <c r="C45" s="19"/>
+      <c r="C45" s="19" t="s">
+        <v>105</v>
+      </c>
       <c r="D45" s="20" t="s">
         <v>68</v>
       </c>
@@ -3912,24 +3936,29 @@
       <c r="F45" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G45" s="37"/>
+      <c r="G45" s="37" t="s">
+        <v>106</v>
+      </c>
       <c r="H45" s="20" t="s">
         <v>88</v>
       </c>
       <c r="I45" s="20"/>
       <c r="J45" s="20"/>
-      <c r="K45" s="21"/>
+      <c r="K45" s="21">
+        <f>7560+11988+7560+71928+2184</f>
+        <v>101220</v>
+      </c>
       <c r="M45" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>10845</v>
       </c>
       <c r="N45" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>90375</v>
       </c>
       <c r="O45" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>903.75</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
@@ -4214,7 +4243,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>2082204</v>
+        <v>2183424</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4222,15 +4251,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>223093.28571428568</v>
+        <v>233938.28571428568</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>1859110.7142857146</v>
+        <v>1949485.7142857146</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>18591.107142857141</v>
+        <v>19494.857142857141</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -4452,7 +4481,9 @@
       <c r="A64">
         <v>5</v>
       </c>
-      <c r="C64" s="19"/>
+      <c r="C64" s="19" t="s">
+        <v>105</v>
+      </c>
       <c r="D64" s="20" t="s">
         <v>68</v>
       </c>
@@ -4460,24 +4491,28 @@
       <c r="F64" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G64" s="37"/>
+      <c r="G64" s="37" t="s">
+        <v>106</v>
+      </c>
       <c r="H64" s="20" t="s">
         <v>88</v>
       </c>
       <c r="I64" s="20"/>
       <c r="J64" s="20"/>
-      <c r="K64" s="21"/>
+      <c r="K64" s="21">
+        <v>5616</v>
+      </c>
       <c r="M64" s="21">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>601.71428571428578</v>
       </c>
       <c r="N64" s="27">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>5014.2857142857138</v>
       </c>
       <c r="O64" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>50.142857142857146</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
@@ -5018,7 +5053,7 @@
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K82" s="44">
         <f>SUM(K61:K81)</f>
-        <v>22518</v>
+        <v>28134</v>
       </c>
       <c r="L82" s="44">
         <f ca="1">SUM(L61:L85)</f>
@@ -5026,15 +5061,15 @@
       </c>
       <c r="M82" s="44">
         <f>SUM(M61:M81)</f>
-        <v>2412.6428571428573</v>
+        <v>3014.3571428571431</v>
       </c>
       <c r="N82" s="44">
         <f>SUM(N61:N81)</f>
-        <v>20105.357142857141</v>
+        <v>25119.642857142855</v>
       </c>
       <c r="O82" s="45">
         <f>SUM(O61:O81)</f>
-        <v>201.05357142857142</v>
+        <v>251.19642857142856</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">

--- a/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FF3897-EB66-44C3-ABD3-3E266C228C25}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077CAF0E-A1B5-4B01-8CB1-5E6ACCAFF319}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
+++ b/GBDS JULY FILES 2026/PURCHASES - JULY 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{077CAF0E-A1B5-4B01-8CB1-5E6ACCAFF319}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAEADF03-D5D1-4C88-BAA7-9AA292C23074}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="111">
   <si>
     <t>HOME MART ENTERPRISES</t>
   </si>
@@ -257,9 +257,6 @@
     <t>NO</t>
   </si>
   <si>
-    <t>06/16/2026</t>
-  </si>
-  <si>
     <t>MONTHLY PURCHASES</t>
   </si>
   <si>
@@ -275,9 +272,6 @@
     <t>MONTHLY PURCHASES SMB LILOY WW</t>
   </si>
   <si>
-    <t>01</t>
-  </si>
-  <si>
     <t>TOTAL AMOUNT</t>
   </si>
   <si>
@@ -354,6 +348,24 @@
   </si>
   <si>
     <t>R12</t>
+  </si>
+  <si>
+    <t>07/28/2026</t>
+  </si>
+  <si>
+    <t>07/27/2026</t>
+  </si>
+  <si>
+    <t>R13</t>
+  </si>
+  <si>
+    <t>R14</t>
+  </si>
+  <si>
+    <t>07/29/2026</t>
+  </si>
+  <si>
+    <t>R15</t>
   </si>
 </sst>
 </file>
@@ -2378,12 +2390,12 @@
     </row>
     <row r="3" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C3" s="41" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D3" s="42"/>
       <c r="E3" s="42"/>
       <c r="F3" s="43" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -2418,10 +2430,10 @@
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J5" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="K5" s="10" t="s">
         <v>3</v>
@@ -2455,10 +2467,10 @@
         <v>10</v>
       </c>
       <c r="I6" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>86</v>
       </c>
       <c r="K6" s="10" t="s">
         <v>11</v>
@@ -2481,7 +2493,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>68</v>
@@ -2494,7 +2506,7 @@
         <v>518825276</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I7" s="21">
         <v>1376614</v>
@@ -2531,7 +2543,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D8" s="20" t="s">
         <v>68</v>
@@ -2544,7 +2556,7 @@
         <v>518829090</v>
       </c>
       <c r="H8" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I8" s="21">
         <v>1354770</v>
@@ -2579,7 +2591,7 @@
         <v>3</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>68</v>
@@ -2592,7 +2604,7 @@
         <v>518839710</v>
       </c>
       <c r="H9" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I9" s="21">
         <f>1397196</f>
@@ -2628,7 +2640,7 @@
         <v>4</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D10" s="20" t="s">
         <v>68</v>
@@ -2641,7 +2653,7 @@
         <v>518843320</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I10" s="21">
         <v>1397196</v>
@@ -2676,7 +2688,7 @@
         <v>5</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>68</v>
@@ -2689,7 +2701,7 @@
         <v>518846972</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I11" s="21">
         <v>1397196</v>
@@ -2724,7 +2736,7 @@
         <v>6</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>68</v>
@@ -2737,7 +2749,7 @@
         <v>518850942</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I12" s="21">
         <v>1397196</v>
@@ -2772,7 +2784,7 @@
         <v>7</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>68</v>
@@ -2785,7 +2797,7 @@
         <v>518851356</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I13" s="21">
         <v>1397196</v>
@@ -2819,7 +2831,9 @@
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="C14" s="19"/>
+      <c r="C14" s="19" t="s">
+        <v>109</v>
+      </c>
       <c r="D14" s="20" t="s">
         <v>68</v>
       </c>
@@ -2827,27 +2841,33 @@
       <c r="F14" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G14" s="20"/>
+      <c r="G14" s="20">
+        <v>518867328</v>
+      </c>
       <c r="H14" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
+        <v>86</v>
+      </c>
+      <c r="I14" s="36">
+        <v>1357955</v>
+      </c>
+      <c r="J14" s="36">
+        <v>74611.91</v>
+      </c>
       <c r="K14" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1283343.0900000001</v>
       </c>
       <c r="M14" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>137501.04535714287</v>
       </c>
       <c r="N14" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>1145842.0446428573</v>
       </c>
       <c r="O14" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>11458.420446428572</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -2859,7 +2879,9 @@
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="C15" s="19"/>
+      <c r="C15" s="19" t="s">
+        <v>109</v>
+      </c>
       <c r="D15" s="20" t="s">
         <v>68</v>
       </c>
@@ -2867,27 +2889,33 @@
       <c r="F15" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G15" s="20"/>
+      <c r="G15" s="20">
+        <v>518867769</v>
+      </c>
       <c r="H15" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="I15" s="21"/>
-      <c r="J15" s="21"/>
+        <v>86</v>
+      </c>
+      <c r="I15" s="21">
+        <v>75215</v>
+      </c>
+      <c r="J15" s="21">
+        <v>9256.9</v>
+      </c>
       <c r="K15" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>65958.100000000006</v>
       </c>
       <c r="M15" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>7066.9392857142866</v>
       </c>
       <c r="N15" s="27">
         <f>K15-M15</f>
-        <v>0</v>
+        <v>58891.160714285717</v>
       </c>
       <c r="O15" s="33">
         <f>K15/112</f>
-        <v>0</v>
+        <v>588.91160714285718</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -2899,7 +2927,9 @@
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="C16" s="19"/>
+      <c r="C16" s="19" t="s">
+        <v>109</v>
+      </c>
       <c r="D16" s="20" t="s">
         <v>68</v>
       </c>
@@ -2907,27 +2937,33 @@
       <c r="F16" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G16" s="20"/>
+      <c r="G16" s="20">
+        <v>518867758</v>
+      </c>
       <c r="H16" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="I16" s="21"/>
-      <c r="J16" s="21"/>
+        <v>86</v>
+      </c>
+      <c r="I16" s="21">
+        <v>1064582</v>
+      </c>
+      <c r="J16" s="21">
+        <v>48308.959999999999</v>
+      </c>
       <c r="K16" s="21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1016273.04</v>
       </c>
       <c r="M16" s="21">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>108886.39714285715</v>
       </c>
       <c r="N16" s="27">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>907386.64285714284</v>
       </c>
       <c r="O16" s="33">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>9073.8664285714294</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -2949,7 +2985,7 @@
       </c>
       <c r="G17" s="20"/>
       <c r="H17" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I17" s="21"/>
       <c r="J17" s="21"/>
@@ -2989,7 +3025,7 @@
       </c>
       <c r="G18" s="20"/>
       <c r="H18" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I18" s="21"/>
       <c r="J18" s="21"/>
@@ -3029,7 +3065,7 @@
       </c>
       <c r="G19" s="20"/>
       <c r="H19" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I19" s="21"/>
       <c r="J19" s="21"/>
@@ -3069,7 +3105,7 @@
       </c>
       <c r="G20" s="20"/>
       <c r="H20" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I20" s="21"/>
       <c r="J20" s="21"/>
@@ -3109,7 +3145,7 @@
       </c>
       <c r="G21" s="20"/>
       <c r="H21" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I21" s="21"/>
       <c r="J21" s="21"/>
@@ -3149,7 +3185,7 @@
       </c>
       <c r="G22" s="20"/>
       <c r="H22" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I22" s="21"/>
       <c r="J22" s="21"/>
@@ -3189,7 +3225,7 @@
       </c>
       <c r="G23" s="20"/>
       <c r="H23" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I23" s="21"/>
       <c r="J23" s="21"/>
@@ -3229,7 +3265,7 @@
       </c>
       <c r="G24" s="20"/>
       <c r="H24" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I24" s="21"/>
       <c r="J24" s="21"/>
@@ -3269,7 +3305,7 @@
       </c>
       <c r="G25" s="20"/>
       <c r="H25" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I25" s="21"/>
       <c r="J25" s="21"/>
@@ -3309,7 +3345,7 @@
       </c>
       <c r="G26" s="20"/>
       <c r="H26" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I26" s="21"/>
       <c r="J26" s="21"/>
@@ -3349,7 +3385,7 @@
       </c>
       <c r="G27" s="20"/>
       <c r="H27" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I27" s="21"/>
       <c r="J27" s="21"/>
@@ -3376,7 +3412,7 @@
       <c r="J28" s="44"/>
       <c r="K28" s="44">
         <f>SUM(K7:K27)</f>
-        <v>9231511.6999999993</v>
+        <v>11597085.93</v>
       </c>
       <c r="L28" s="44">
         <f ca="1">SUM(L7:L31)</f>
@@ -3384,15 +3420,15 @@
       </c>
       <c r="M28" s="44">
         <f>SUM(M7:M27)</f>
-        <v>989090.53928571416</v>
+        <v>1242544.9210714283</v>
       </c>
       <c r="N28" s="44">
         <f>SUM(N7:N27)</f>
-        <v>8242421.1607142854</v>
+        <v>10354541.008928571</v>
       </c>
       <c r="O28" s="44">
         <f>SUM(O7:O27)</f>
-        <v>82424.211607142861</v>
+        <v>103545.41008928572</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -3401,12 +3437,12 @@
     </row>
     <row r="30" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C30" s="41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D30" s="42"/>
       <c r="E30" s="42"/>
       <c r="F30" s="43" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
@@ -3441,10 +3477,10 @@
       </c>
       <c r="H32" s="9"/>
       <c r="I32" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J32" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="J32" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="K32" s="10" t="s">
         <v>3</v>
@@ -3478,10 +3514,10 @@
         <v>10</v>
       </c>
       <c r="I33" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J33" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>86</v>
       </c>
       <c r="K33" s="10" t="s">
         <v>11</v>
@@ -3511,10 +3547,10 @@
         <v>70</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H34" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I34" s="20"/>
       <c r="J34" s="20"/>
@@ -3550,10 +3586,10 @@
         <v>70</v>
       </c>
       <c r="G35" s="37" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H35" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I35" s="20"/>
       <c r="J35" s="20"/>
@@ -3588,10 +3624,10 @@
         <v>70</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H36" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I36" s="20"/>
       <c r="J36" s="20"/>
@@ -3626,10 +3662,10 @@
         <v>70</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="H37" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I37" s="20"/>
       <c r="J37" s="20"/>
@@ -3654,7 +3690,7 @@
         <v>6</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D38" s="20" t="s">
         <v>68</v>
@@ -3664,10 +3700,10 @@
         <v>70</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H38" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I38" s="20"/>
       <c r="J38" s="20"/>
@@ -3693,7 +3729,7 @@
         <v>7</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D39" s="20" t="s">
         <v>68</v>
@@ -3703,10 +3739,10 @@
         <v>70</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="H39" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I39" s="20"/>
       <c r="J39" s="20"/>
@@ -3732,7 +3768,7 @@
         <v>8</v>
       </c>
       <c r="C40" s="19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D40" s="20" t="s">
         <v>68</v>
@@ -3742,10 +3778,10 @@
         <v>70</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H40" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I40" s="20"/>
       <c r="J40" s="20"/>
@@ -3771,7 +3807,7 @@
         <v>9</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>68</v>
@@ -3781,10 +3817,10 @@
         <v>70</v>
       </c>
       <c r="G41" s="37" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H41" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I41" s="20"/>
       <c r="J41" s="20"/>
@@ -3810,7 +3846,7 @@
         <v>10</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D42" s="20" t="s">
         <v>68</v>
@@ -3820,10 +3856,10 @@
         <v>70</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H42" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I42" s="20"/>
       <c r="J42" s="20"/>
@@ -3849,7 +3885,7 @@
         <v>11</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D43" s="20" t="s">
         <v>68</v>
@@ -3859,10 +3895,10 @@
         <v>70</v>
       </c>
       <c r="G43" s="37" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H43" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I43" s="20"/>
       <c r="J43" s="20"/>
@@ -3888,7 +3924,7 @@
         <v>12</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D44" s="20" t="s">
         <v>68</v>
@@ -3898,10 +3934,10 @@
         <v>70</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H44" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I44" s="20"/>
       <c r="J44" s="20"/>
@@ -3927,7 +3963,7 @@
         <v>13</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D45" s="20" t="s">
         <v>68</v>
@@ -3937,10 +3973,10 @@
         <v>70</v>
       </c>
       <c r="G45" s="37" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H45" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I45" s="20"/>
       <c r="J45" s="20"/>
@@ -3965,7 +4001,9 @@
       <c r="A46">
         <v>14</v>
       </c>
-      <c r="C46" s="19"/>
+      <c r="C46" s="19" t="s">
+        <v>106</v>
+      </c>
       <c r="D46" s="20" t="s">
         <v>68</v>
       </c>
@@ -3973,31 +4011,38 @@
       <c r="F46" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G46" s="37"/>
+      <c r="G46" s="37" t="s">
+        <v>107</v>
+      </c>
       <c r="H46" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I46" s="20"/>
       <c r="J46" s="20"/>
-      <c r="K46" s="21"/>
+      <c r="K46" s="21">
+        <f>7560+10656+179820</f>
+        <v>198036</v>
+      </c>
       <c r="M46" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>21218.142857142855</v>
       </c>
       <c r="N46" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>176817.85714285716</v>
       </c>
       <c r="O46" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1768.1785714285713</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>15</v>
       </c>
-      <c r="C47" s="19"/>
+      <c r="C47" s="19" t="s">
+        <v>105</v>
+      </c>
       <c r="D47" s="20" t="s">
         <v>68</v>
       </c>
@@ -4005,31 +4050,38 @@
       <c r="F47" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G47" s="37"/>
+      <c r="G47" s="37" t="s">
+        <v>108</v>
+      </c>
       <c r="H47" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I47" s="20"/>
       <c r="J47" s="20"/>
-      <c r="K47" s="21"/>
+      <c r="K47" s="21">
+        <f>23976+119880+9072</f>
+        <v>152928</v>
+      </c>
       <c r="M47" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>16385.142857142855</v>
       </c>
       <c r="N47" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>136542.85714285716</v>
       </c>
       <c r="O47" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1365.4285714285713</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>16</v>
       </c>
-      <c r="C48" s="19"/>
+      <c r="C48" s="19" t="s">
+        <v>109</v>
+      </c>
       <c r="D48" s="20" t="s">
         <v>68</v>
       </c>
@@ -4037,24 +4089,29 @@
       <c r="F48" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G48" s="37"/>
+      <c r="G48" s="37" t="s">
+        <v>110</v>
+      </c>
       <c r="H48" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I48" s="20"/>
       <c r="J48" s="20"/>
-      <c r="K48" s="21"/>
+      <c r="K48" s="21">
+        <f>11988+119880</f>
+        <v>131868</v>
+      </c>
       <c r="M48" s="21">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>14128.714285714286</v>
       </c>
       <c r="N48" s="27">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>117739.28571428571</v>
       </c>
       <c r="O48" s="33">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1177.3928571428571</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
@@ -4071,7 +4128,7 @@
       </c>
       <c r="G49" s="37"/>
       <c r="H49" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I49" s="20"/>
       <c r="J49" s="20"/>
@@ -4103,7 +4160,7 @@
       </c>
       <c r="G50" s="37"/>
       <c r="H50" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I50" s="20"/>
       <c r="J50" s="20"/>
@@ -4135,7 +4192,7 @@
       </c>
       <c r="G51" s="37"/>
       <c r="H51" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I51" s="20"/>
       <c r="J51" s="20"/>
@@ -4167,7 +4224,7 @@
       </c>
       <c r="G52" s="37"/>
       <c r="H52" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I52" s="20"/>
       <c r="J52" s="20"/>
@@ -4199,7 +4256,7 @@
       </c>
       <c r="G53" s="37"/>
       <c r="H53" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I53" s="20"/>
       <c r="J53" s="20"/>
@@ -4231,7 +4288,7 @@
       </c>
       <c r="G54" s="37"/>
       <c r="H54" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I54" s="20"/>
       <c r="J54" s="20"/>
@@ -4243,7 +4300,7 @@
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K55" s="44">
         <f>SUM(K34:K54)</f>
-        <v>2183424</v>
+        <v>2666256</v>
       </c>
       <c r="L55" s="44">
         <f ca="1">SUM(L34:L58)</f>
@@ -4251,15 +4308,15 @@
       </c>
       <c r="M55" s="44">
         <f>SUM(M34:M54)</f>
-        <v>233938.28571428568</v>
+        <v>285670.28571428562</v>
       </c>
       <c r="N55" s="44">
         <f>SUM(N34:N54)</f>
-        <v>1949485.7142857146</v>
+        <v>2380585.714285715</v>
       </c>
       <c r="O55" s="45">
         <f>SUM(O34:O54)</f>
-        <v>19494.857142857141</v>
+        <v>23805.857142857145</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -4267,12 +4324,12 @@
     </row>
     <row r="57" spans="1:15" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C57" s="41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D57" s="42"/>
       <c r="E57" s="42"/>
       <c r="F57" s="43" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G57" s="1"/>
       <c r="H57" s="1"/>
@@ -4307,10 +4364,10 @@
       </c>
       <c r="H59" s="9"/>
       <c r="I59" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J59" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="J59" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="K59" s="10" t="s">
         <v>3</v>
@@ -4344,10 +4401,10 @@
         <v>10</v>
       </c>
       <c r="I60" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J60" s="9" t="s">
         <v>84</v>
-      </c>
-      <c r="J60" s="9" t="s">
-        <v>86</v>
       </c>
       <c r="K60" s="10" t="s">
         <v>11</v>
@@ -4367,7 +4424,7 @@
         <v>2</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D61" s="20" t="s">
         <v>68</v>
@@ -4377,10 +4434,10 @@
         <v>70</v>
       </c>
       <c r="G61" s="37" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I61" s="20"/>
       <c r="J61" s="20"/>
@@ -4406,7 +4463,7 @@
         <v>3</v>
       </c>
       <c r="C62" s="19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D62" s="20" t="s">
         <v>68</v>
@@ -4416,10 +4473,10 @@
         <v>70</v>
       </c>
       <c r="G62" s="37" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H62" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I62" s="20"/>
       <c r="J62" s="20"/>
@@ -4444,7 +4501,7 @@
         <v>4</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D63" s="20" t="s">
         <v>68</v>
@@ -4454,10 +4511,10 @@
         <v>70</v>
       </c>
       <c r="G63" s="37" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="H63" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I63" s="20"/>
       <c r="J63" s="20"/>
@@ -4482,7 +4539,7 @@
         <v>5</v>
       </c>
       <c r="C64" s="19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D64" s="20" t="s">
         <v>68</v>
@@ -4492,10 +4549,10 @@
         <v>70</v>
       </c>
       <c r="G64" s="37" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="H64" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I64" s="20"/>
       <c r="J64" s="20"/>
@@ -4519,7 +4576,9 @@
       <c r="A65">
         <v>6</v>
       </c>
-      <c r="C65" s="19"/>
+      <c r="C65" s="19" t="s">
+        <v>105</v>
+      </c>
       <c r="D65" s="20" t="s">
         <v>68</v>
       </c>
@@ -4527,31 +4586,37 @@
       <c r="F65" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G65" s="37"/>
+      <c r="G65" s="37" t="s">
+        <v>108</v>
+      </c>
       <c r="H65" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I65" s="20"/>
       <c r="J65" s="20"/>
-      <c r="K65" s="21"/>
+      <c r="K65" s="21">
+        <v>5670</v>
+      </c>
       <c r="M65" s="21">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>607.5</v>
       </c>
       <c r="N65" s="27">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>5062.5</v>
       </c>
       <c r="O65" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>50.625</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>7</v>
       </c>
-      <c r="C66" s="19"/>
+      <c r="C66" s="19" t="s">
+        <v>109</v>
+      </c>
       <c r="D66" s="20" t="s">
         <v>68</v>
       </c>
@@ -4559,24 +4624,28 @@
       <c r="F66" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G66" s="37"/>
+      <c r="G66" s="37" t="s">
+        <v>110</v>
+      </c>
       <c r="H66" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I66" s="20"/>
       <c r="J66" s="20"/>
-      <c r="K66" s="21"/>
+      <c r="K66" s="21">
+        <v>5616</v>
+      </c>
       <c r="M66" s="21">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>601.71428571428578</v>
       </c>
       <c r="N66" s="27">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>5014.2857142857138</v>
       </c>
       <c r="O66" s="33">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>50.142857142857146</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
@@ -4593,7 +4662,7 @@
       </c>
       <c r="G67" s="37"/>
       <c r="H67" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I67" s="20"/>
       <c r="J67" s="20"/>
@@ -4625,7 +4694,7 @@
       </c>
       <c r="G68" s="37"/>
       <c r="H68" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I68" s="20"/>
       <c r="J68" s="20"/>
@@ -4657,7 +4726,7 @@
       </c>
       <c r="G69" s="37"/>
       <c r="H69" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I69" s="20"/>
       <c r="J69" s="20"/>
@@ -4689,7 +4758,7 @@
       </c>
       <c r="G70" s="37"/>
       <c r="H70" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I70" s="20"/>
       <c r="J70" s="20"/>
@@ -4721,7 +4790,7 @@
       </c>
       <c r="G71" s="37"/>
       <c r="H71" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I71" s="20"/>
       <c r="J71" s="20"/>
@@ -4753,7 +4822,7 @@
       </c>
       <c r="G72" s="37"/>
       <c r="H72" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I72" s="20"/>
       <c r="J72" s="20"/>
@@ -4785,7 +4854,7 @@
       </c>
       <c r="G73" s="37"/>
       <c r="H73" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I73" s="20"/>
       <c r="J73" s="20"/>
@@ -4817,7 +4886,7 @@
       </c>
       <c r="G74" s="37"/>
       <c r="H74" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I74" s="20"/>
       <c r="J74" s="20"/>
@@ -4849,7 +4918,7 @@
       </c>
       <c r="G75" s="37"/>
       <c r="H75" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I75" s="20"/>
       <c r="J75" s="20"/>
@@ -4881,7 +4950,7 @@
       </c>
       <c r="G76" s="37"/>
       <c r="H76" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I76" s="20"/>
       <c r="J76" s="20"/>
@@ -4913,7 +4982,7 @@
       </c>
       <c r="G77" s="37"/>
       <c r="H77" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I77" s="20"/>
       <c r="J77" s="20"/>
@@ -4945,7 +5014,7 @@
       </c>
       <c r="G78" s="37"/>
       <c r="H78" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I78" s="20"/>
       <c r="J78" s="20"/>
@@ -4977,7 +5046,7 @@
       </c>
       <c r="G79" s="37"/>
       <c r="H79" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I79" s="20"/>
       <c r="J79" s="20"/>
@@ -5009,7 +5078,7 @@
       </c>
       <c r="G80" s="37"/>
       <c r="H80" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I80" s="20"/>
       <c r="J80" s="20"/>
@@ -5041,7 +5110,7 @@
       </c>
       <c r="G81" s="37"/>
       <c r="H81" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I81" s="20"/>
       <c r="J81" s="20"/>
@@ -5053,7 +5122,7 @@
     <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K82" s="44">
         <f>SUM(K61:K81)</f>
-        <v>28134</v>
+        <v>39420</v>
       </c>
       <c r="L82" s="44">
         <f ca="1">SUM(L61:L85)</f>
@@ -5061,25 +5130,25 @@
       </c>
       <c r="M82" s="44">
         <f>SUM(M61:M81)</f>
-        <v>3014.3571428571431</v>
+        <v>4223.5714285714294</v>
       </c>
       <c r="N82" s="44">
         <f>SUM(N61:N81)</f>
-        <v>25119.642857142855</v>
+        <v>35196.428571428565</v>
       </c>
       <c r="O82" s="45">
         <f>SUM(O61:O81)</f>
-        <v>251.19642857142856</v>
+        <v>351.96428571428572</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="C84" s="41" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D84" s="42"/>
       <c r="E84" s="42"/>
       <c r="F84" s="43" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
@@ -5114,10 +5183,10 @@
       </c>
       <c r="H86" s="9"/>
       <c r="I86" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="J86" s="9" t="s">
         <v>83</v>
-      </c>
-      <c r="J86" s="9" t="s">
-        <v>85</v>
       </c>
       <c r="M86" s="10" t="s">
         <v>3</v>
@@ -5151,13 +5220,13 @@
         <v>10</v>
       </c>
       <c r="I87" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="J87" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="J87" s="9" t="s">
-        <v>86</v>
-      </c>
       <c r="K87" s="46" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="M87" s="10" t="s">
         <v>11</v>
@@ -5176,9 +5245,7 @@
       <c r="A88">
         <v>2</v>
       </c>
-      <c r="C88" s="19" t="s">
-        <v>74</v>
-      </c>
+      <c r="C88" s="19"/>
       <c r="D88" s="20" t="s">
         <v>68</v>
       </c>
@@ -5186,32 +5253,26 @@
       <c r="F88" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="G88" s="37" t="s">
-        <v>80</v>
-      </c>
+      <c r="G88" s="37"/>
       <c r="H88" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I88" s="20"/>
       <c r="J88" s="20"/>
-      <c r="K88" s="21">
-        <v>1608</v>
-      </c>
+      <c r="K88" s="21"/>
       <c r="L88" s="21"/>
-      <c r="M88" s="21">
-        <v>16488</v>
-      </c>
+      <c r="M88" s="21"/>
       <c r="N88" s="21">
         <f t="shared" ref="N88:N107" si="14">P88*12</f>
-        <v>1766.5714285714287</v>
+        <v>0</v>
       </c>
       <c r="O88" s="27">
         <f t="shared" ref="O88:O107" si="15">M88-N88</f>
-        <v>14721.428571428571</v>
+        <v>0</v>
       </c>
       <c r="P88" s="33">
         <f t="shared" ref="P88:P107" si="16">M88/112</f>
-        <v>147.21428571428572</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.25">
@@ -5228,7 +5289,7 @@
       </c>
       <c r="G89" s="37"/>
       <c r="H89" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I89" s="20"/>
       <c r="J89" s="20"/>
@@ -5262,7 +5323,7 @@
       </c>
       <c r="G90" s="37"/>
       <c r="H90" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I90" s="20"/>
       <c r="J90" s="20"/>
@@ -5296,7 +5357,7 @@
       </c>
       <c r="G91" s="37"/>
       <c r="H91" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I91" s="20"/>
       <c r="J91" s="20"/>
@@ -5330,7 +5391,7 @@
       </c>
       <c r="G92" s="37"/>
       <c r="H92" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I92" s="20"/>
       <c r="J92" s="20"/>
@@ -5364,7 +5425,7 @@
       </c>
       <c r="G93" s="37"/>
       <c r="H93" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I93" s="20"/>
       <c r="J93" s="20"/>
@@ -5398,7 +5459,7 @@
       </c>
       <c r="G94" s="37"/>
       <c r="H94" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I94" s="20"/>
       <c r="J94" s="20"/>
@@ -5432,7 +5493,7 @@
       </c>
       <c r="G95" s="37"/>
       <c r="H95" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I95" s="20"/>
       <c r="J95" s="20"/>
@@ -5466,7 +5527,7 @@
       </c>
       <c r="G96" s="37"/>
       <c r="H96" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I96" s="20"/>
       <c r="J96" s="20"/>
@@ -5500,7 +5561,7 @@
       </c>
       <c r="G97" s="37"/>
       <c r="H97" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I97" s="20"/>
       <c r="J97" s="20"/>
@@ -5534,7 +5595,7 @@
       </c>
       <c r="G98" s="37"/>
       <c r="H98" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I98" s="20"/>
       <c r="J98" s="20"/>
@@ -5568,7 +5629,7 @@
       </c>
       <c r="G99" s="37"/>
       <c r="H99" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I99" s="20"/>
       <c r="J99" s="20"/>
@@ -5602,7 +5663,7 @@
       </c>
       <c r="G100" s="37"/>
       <c r="H100" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I100" s="20"/>
       <c r="J100" s="20"/>
@@ -5636,7 +5697,7 @@
       </c>
       <c r="G101" s="37"/>
       <c r="H101" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I101" s="20"/>
       <c r="J101" s="20"/>
@@ -5670,7 +5731,7 @@
       </c>
       <c r="G102" s="37"/>
       <c r="H102" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I102" s="20"/>
       <c r="J102" s="20"/>
@@ -5704,7 +5765,7 @@
       </c>
       <c r="G103" s="37"/>
       <c r="H103" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I103" s="20"/>
       <c r="J103" s="20"/>
@@ -5738,7 +5799,7 @@
       </c>
       <c r="G104" s="37"/>
       <c r="H104" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I104" s="20"/>
       <c r="J104" s="20"/>
@@ -5772,7 +5833,7 @@
       </c>
       <c r="G105" s="37"/>
       <c r="H105" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I105" s="20"/>
       <c r="J105" s="20"/>
@@ -5806,7 +5867,7 @@
       </c>
       <c r="G106" s="37"/>
       <c r="H106" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I106" s="20"/>
       <c r="J106" s="20"/>
@@ -5840,7 +5901,7 @@
       </c>
       <c r="G107" s="37"/>
       <c r="H107" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I107" s="20"/>
       <c r="J107" s="20"/>
@@ -5874,7 +5935,7 @@
       </c>
       <c r="G108" s="37"/>
       <c r="H108" s="20" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I108" s="20"/>
       <c r="J108" s="20"/>
@@ -5888,7 +5949,7 @@
     <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K109" s="44">
         <f>SUM(K88:K108)</f>
-        <v>1608</v>
+        <v>0</v>
       </c>
       <c r="L109" s="44">
         <f ca="1">SUM(L88:L112)</f>
@@ -5896,19 +5957,19 @@
       </c>
       <c r="M109" s="44">
         <f>SUM(M88:M108)</f>
-        <v>16488</v>
+        <v>0</v>
       </c>
       <c r="N109" s="44">
         <f>SUM(N88:N108)</f>
-        <v>1766.5714285714287</v>
+        <v>0</v>
       </c>
       <c r="O109" s="45">
         <f>SUM(O88:O108)</f>
-        <v>14721.428571428571</v>
+        <v>0</v>
       </c>
       <c r="P109" s="45">
         <f>SUM(P88:P108)</f>
-        <v>147.21428571428572</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
